--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487857_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487857_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8441</v>
+        <v>4.681</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1896</v>
+        <v>5.3201</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3455</v>
+        <v>-0.6391</v>
       </c>
       <c r="G2" t="n">
         <v>0.4584</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09329999999999999</v>
+        <v>-0.0698</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1214</v>
+        <v>0.0091</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2147</v>
+        <v>-0.0789</v>
       </c>
       <c r="V2" t="n">
         <v>2.2112</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7314</v>
+        <v>3.8032</v>
       </c>
       <c r="E3" t="n">
-        <v>3.886</v>
+        <v>4.0164</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1546</v>
+        <v>-0.2133</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0922</v>
@@ -688,13 +688,13 @@
         <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4678</v>
+        <v>-0.396</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.37</v>
+        <v>-0.2395</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0978</v>
+        <v>-0.1565</v>
       </c>
       <c r="V3" t="n">
         <v>3.0427</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>P. MARTIN MARTIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9405</v>
+        <v>3.4176</v>
       </c>
       <c r="E4" t="n">
-        <v>4.108</v>
+        <v>2.3454</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1676</v>
+        <v>1.0722</v>
       </c>
       <c r="G4" t="n">
-        <v>1.433</v>
+        <v>1.4672</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1663</v>
+        <v>0.6695</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7333</v>
+        <v>0.7976</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4498</v>
+        <v>2.2837</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0849</v>
+        <v>1.2044</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3649</v>
+        <v>1.0793</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0168</v>
+        <v>-0.8166</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0814</v>
+        <v>-0.5349</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0982</v>
+        <v>-0.2817</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07240000000000001</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6582</v>
+        <v>-0.2952</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5858</v>
+        <v>0.2238</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARTIN MARTIN</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7857</v>
+        <v>2.3548</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0658</v>
+        <v>3.7866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7199</v>
+        <v>-1.4318</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4672</v>
+        <v>1.433</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6695</v>
+        <v>3.1663</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7976</v>
+        <v>-1.7333</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2837</v>
+        <v>3.4498</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2044</v>
+        <v>3.0849</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0793</v>
+        <v>0.3649</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8166</v>
+        <v>-2.0168</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5349</v>
+        <v>0.0814</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>-2.0982</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7033</v>
+        <v>-0.5133</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5748</v>
+        <v>0.3367</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1285</v>
+        <v>-0.85</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OCHI</t>
+          <t>J. HANNA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1473</v>
+        <v>0.9877</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8341</v>
+        <v>3.5205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3133</v>
+        <v>-2.5328</v>
       </c>
       <c r="G6" t="n">
-        <v>2.375</v>
+        <v>1.098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4115</v>
+        <v>3.3644</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9635</v>
+        <v>-2.2664</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1019</v>
+        <v>2.6372</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1425</v>
+        <v>3.234</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9594</v>
+        <v>-0.5968</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7269</v>
+        <v>-1.5391</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.731</v>
+        <v>0.1304</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0041</v>
+        <v>-1.6696</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.4568</v>
+        <v>1.8731</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8129</v>
+        <v>-0.4621</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8539</v>
+        <v>0.0696</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.041</v>
+        <v>-0.5317</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5838</v>
+        <v>-1.5213</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5838</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. HANNA</t>
+          <t>M. OCHI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4542</v>
+        <v>0.4984</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1338</v>
+        <v>0.2145</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6796</v>
+        <v>0.2839</v>
       </c>
       <c r="G7" t="n">
-        <v>1.098</v>
+        <v>2.375</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3644</v>
+        <v>0.4115</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2664</v>
+        <v>1.9635</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6372</v>
+        <v>3.1019</v>
       </c>
       <c r="K7" t="n">
-        <v>3.234</v>
+        <v>1.1425</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5968</v>
+        <v>1.9594</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5391</v>
+        <v>-0.7269</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1304</v>
+        <v>-0.731</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6696</v>
+        <v>0.0041</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8731</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9956</v>
+        <v>0.1639</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3171</v>
+        <v>0.2343</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6785</v>
+        <v>-0.0704</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5213</v>
+        <v>-0.5838</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3351</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2983</v>
+        <v>0.4936</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.7331</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1386</v>
+        <v>1.2266</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2976</v>
@@ -1078,13 +1078,13 @@
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4228</v>
+        <v>-0.2275</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1618</v>
+        <v>-0.0737</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0371</v>
+        <v>0.0216</v>
       </c>
       <c r="E9" t="n">
         <v>1.1812</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2183</v>
+        <v>-1.1596</v>
       </c>
       <c r="G9" t="n">
         <v>0.8461</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2995</v>
+        <v>-0.2407</v>
       </c>
       <c r="T9" t="n">
         <v>-0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5838</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9957</v>
+        <v>-1.2083</v>
       </c>
       <c r="E10" t="n">
-        <v>0.434</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4297</v>
+        <v>-2.1361</v>
       </c>
       <c r="G10" t="n">
         <v>1.939</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8078</v>
+        <v>-1.0204</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5748</v>
+        <v>-0.0809</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.233</v>
+        <v>-0.9394</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3351</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2743</v>
+        <v>-6.5026</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4392</v>
+        <v>-6.3739</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1649</v>
+        <v>-0.1287</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6743</v>
@@ -1312,13 +1312,13 @@
         <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1462</v>
+        <v>-0.0822</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0743</v>
+        <v>0.1396</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0718</v>
+        <v>-0.2217</v>
       </c>
       <c r="V11" t="n">
         <v>0.5838</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.894400000000001</v>
+        <v>8.547000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>13.5531</v>
+        <v>14.2056</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.6586</v>
+        <v>-5.6587</v>
       </c>
       <c r="G12" t="n">
         <v>5.5526</v>
@@ -1390,13 +1390,13 @@
         <v>15.6088</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.572000000000001</v>
+        <v>-2.9195</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6856</v>
+        <v>-0.033</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8865</v>
+        <v>-2.8864</v>
       </c>
       <c r="V12" t="n">
         <v>1.7512</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.005599999999999</v>
+        <v>6.837</v>
       </c>
       <c r="E13" t="n">
-        <v>9.048299999999999</v>
+        <v>7.2457</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0427</v>
+        <v>-0.4086</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6053</v>
+        <v>3.6184</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0149</v>
+        <v>1.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5904</v>
+        <v>2.0084</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7939</v>
+        <v>5.9333</v>
       </c>
       <c r="K13" t="n">
-        <v>3.138</v>
+        <v>3.1085</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6558</v>
+        <v>2.8248</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1886</v>
+        <v>-2.3149</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1231</v>
+        <v>-1.4985</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0654</v>
+        <v>-0.8164</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6649</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R13" t="n">
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5679</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.087</v>
+        <v>-0.109</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4809</v>
+        <v>0.1175</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1675</v>
+        <v>3.6264</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1675</v>
+        <v>3.5026</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5727</v>
+        <v>6.5397</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3884</v>
+        <v>7.7625</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8158</v>
+        <v>-1.2228</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6184</v>
+        <v>2.6053</v>
       </c>
       <c r="H14" t="n">
-        <v>1.61</v>
+        <v>1.0149</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0084</v>
+        <v>1.5904</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9333</v>
+        <v>5.7939</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1085</v>
+        <v>3.138</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8248</v>
+        <v>2.6558</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3149</v>
+        <v>-3.1886</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4985</v>
+        <v>-2.1231</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8164</v>
+        <v>-1.0654</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2559</v>
+        <v>1.1019</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9663</v>
+        <v>0.8011</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2896</v>
+        <v>0.3008</v>
       </c>
       <c r="V14" t="n">
-        <v>3.6264</v>
+        <v>1.1675</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5026</v>
+        <v>1.1675</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2713</v>
+        <v>1.3888</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8767</v>
+        <v>2.7339</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6054</v>
+        <v>-1.3451</v>
       </c>
       <c r="G15" t="n">
         <v>0.9602000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3133</v>
+        <v>-0.1957</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0315</v>
+        <v>-0.1743</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2818</v>
+        <v>-0.0215</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4813</v>
+        <v>-0.267</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1352</v>
+        <v>0.3495</v>
       </c>
       <c r="F16" t="n">
         <v>-0.6165</v>
@@ -1702,10 +1702,10 @@
         <v>0.2081</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2081</v>
+        <v>0.0062</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0776</v>
+        <v>0.2919</v>
       </c>
       <c r="U16" t="n">
         <v>-0.2857</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1997</v>
+        <v>-1.3974</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5845</v>
+        <v>-1.0131</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6152</v>
+        <v>-0.3843</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4507</v>
@@ -1780,13 +1780,13 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7078</v>
+        <v>0.5102</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7268</v>
+        <v>0.2981</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0189</v>
+        <v>0.212</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.188</v>
+        <v>-1.6355</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6191</v>
+        <v>-1.2976</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5689</v>
+        <v>-0.3379</v>
       </c>
       <c r="G18" t="n">
         <v>-0.523</v>
@@ -1858,13 +1858,13 @@
         <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1487</v>
+        <v>0.7012</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1214</v>
+        <v>0.2001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2701</v>
+        <v>0.5011</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3975</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7678</v>
+        <v>-2.3979</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8487</v>
+        <v>-2.4201</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0809</v>
+        <v>0.0221</v>
       </c>
       <c r="G19" t="n">
         <v>-2.9992</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2473</v>
+        <v>0.1226</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7177</v>
+        <v>-0.2891</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4704</v>
+        <v>0.4117</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3538</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1658</v>
+        <v>-2.7557</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5042</v>
+        <v>-2.5306</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6616</v>
+        <v>-0.2251</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.7389</v>
+        <v>-0.0408</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7656</v>
+        <v>0.7037</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9733</v>
+        <v>-0.7446</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7057</v>
+        <v>0.3226</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2265</v>
+        <v>0.9978</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4792</v>
+        <v>-0.6752</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0331</v>
+        <v>-0.3634</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5391</v>
+        <v>-0.294</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.494</v>
+        <v>-0.0694</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-3.1218</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5325</v>
+        <v>0.4069</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2421</v>
+        <v>0.2686</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2904</v>
+        <v>0.1383</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4216</v>
+        <v>-3.5103</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.852</v>
+        <v>-1.9329</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5696</v>
+        <v>-1.5774</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0408</v>
+        <v>-3.7389</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7037</v>
+        <v>-1.7656</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7446</v>
+        <v>-1.9733</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3226</v>
+        <v>-1.7057</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9978</v>
+        <v>-1.2265</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6752</v>
+        <v>-0.4792</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3634</v>
+        <v>-2.0331</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.294</v>
+        <v>-0.5391</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0694</v>
+        <v>-1.494</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1218</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.259</v>
+        <v>1.188</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0529</v>
+        <v>0.8135</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2061</v>
+        <v>0.3745</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0745</v>
+        <v>-4.4571</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0574</v>
+        <v>-1.7004</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0171</v>
+        <v>-2.7568</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4948</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7522</v>
+        <v>0.3696</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9192</v>
+        <v>0.2763</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.167</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2914</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4453</v>
+        <v>-4.8103</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3241</v>
+        <v>-1.5384</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1212</v>
+        <v>-3.2719</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0078</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1463</v>
+        <v>0.7813</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7235</v>
+        <v>0.5091</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4228</v>
+        <v>0.2721</v>
       </c>
       <c r="V23" t="n">
         <v>-2.3351</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.894400000000003</v>
+        <v>-6.465699999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>5.6586</v>
+        <v>5.658499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.5531</v>
+        <v>-12.1243</v>
       </c>
       <c r="G24" t="n">
         <v>-5.5526</v>
@@ -2305,7 +2305,7 @@
         <v>2.981999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>9.225600000000002</v>
+        <v>9.2256</v>
       </c>
       <c r="M24" t="n">
         <v>-17.7601</v>
@@ -2314,7 +2314,7 @@
         <v>-12.0859</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.673900000000001</v>
+        <v>-5.6739</v>
       </c>
       <c r="P24" t="n">
         <v>-4.1623</v>
@@ -2326,13 +2326,13 @@
         <v>11.4464</v>
       </c>
       <c r="S24" t="n">
-        <v>3.571800000000001</v>
+        <v>5.0007</v>
       </c>
       <c r="T24" t="n">
-        <v>2.886400000000001</v>
+        <v>2.8863</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6855</v>
+        <v>2.1141</v>
       </c>
       <c r="V24" t="n">
         <v>-1.751400000000001</v>
